--- a/In3Days/CHP3-DEM/Pedestrian Airport modelling/Flights.xlsx
+++ b/In3Days/CHP3-DEM/Pedestrian Airport modelling/Flights.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wsp\Training Materials\Extras\Models\Airport Book 5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acctecho365-my.sharepoint.com/personal/wilco_sievers_4sight_cloud/Documents/Documents/AnyLogic/In3Days/CHP3-DEM/Pedestrian Airport modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_FBFE21995ACCDC36C0378A268E4A4AE5C1399CD5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6724CBE1-C2B6-4F10-A7E8-FDD5E2BF4C16}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="150" windowWidth="25875" windowHeight="11055"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -69,7 +70,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
@@ -156,23 +157,23 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный_Лист1" xfId="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный_Лист1" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -188,9 +189,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -228,9 +229,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -265,7 +266,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -300,7 +301,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -473,15 +474,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +493,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -503,7 +504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -514,7 +515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -525,7 +526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -536,7 +537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -547,78 +548,78 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="6">
-        <v>41994.71875</v>
+        <v>41994.677083333336</v>
       </c>
       <c r="C7" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="6">
-        <v>41994.739583333336</v>
+        <v>41994.697916666664</v>
       </c>
       <c r="C8" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="6">
-        <v>41994.777777777781</v>
+        <v>41994.569444444445</v>
       </c>
       <c r="C9" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="6">
-        <v>41994.809027777781</v>
+        <v>41994.600694444445</v>
       </c>
       <c r="C10" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="6">
-        <v>41994.854166666664</v>
+        <v>41994.520833333336</v>
       </c>
       <c r="C11" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="6">
-        <v>41994.895833333336</v>
+        <v>41994.604166666664</v>
       </c>
       <c r="C12" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="6">
-        <v>41994.930555555555</v>
+        <v>41994.680555555555</v>
       </c>
       <c r="C13" s="5">
         <v>1</v>
